--- a/Deliverables/BOM/eSpark_BOM_Stepper_Breakout.xlsx
+++ b/Deliverables/BOM/eSpark_BOM_Stepper_Breakout.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Mahmood-PTZKeyboard\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FD4FE30-9B79-4E2D-A12C-0F48427299EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38CA05D1-A33B-45CF-9B24-B933DE610589}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="230">
   <si>
     <t>Component list</t>
   </si>
@@ -1354,30 +1354,6 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1419,6 +1395,12 @@
     </xf>
     <xf numFmtId="0" fontId="23" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="3" borderId="15" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1428,11 +1410,29 @@
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="166" fontId="15" fillId="3" borderId="15" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="15" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1810,15 +1810,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="58"/>
-      <c r="L1" s="58"/>
-      <c r="M1" s="58"/>
-      <c r="N1" s="58"/>
-      <c r="O1" s="58"/>
-      <c r="P1" s="58"/>
-      <c r="Q1" s="58"/>
-      <c r="R1" s="58"/>
-      <c r="S1" s="59"/>
+      <c r="K1" s="76"/>
+      <c r="L1" s="76"/>
+      <c r="M1" s="76"/>
+      <c r="N1" s="76"/>
+      <c r="O1" s="76"/>
+      <c r="P1" s="76"/>
+      <c r="Q1" s="76"/>
+      <c r="R1" s="76"/>
+      <c r="S1" s="77"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -1868,7 +1868,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="60"/>
+      <c r="S3" s="78"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -1893,7 +1893,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="61"/>
+      <c r="S4" s="79"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -1918,7 +1918,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="61"/>
+      <c r="S5" s="79"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -1939,7 +1939,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="61"/>
+      <c r="S6" s="79"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -1960,7 +1960,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="61"/>
+      <c r="S7" s="79"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -1981,7 +1981,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="61"/>
+      <c r="S8" s="79"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -2046,7 +2046,7 @@
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="66" t="s">
+      <c r="C10" s="58" t="s">
         <v>166</v>
       </c>
       <c r="D10" s="46" t="s">
@@ -2083,13 +2083,13 @@
       <c r="N10" s="46">
         <v>150</v>
       </c>
-      <c r="O10" s="71" t="s">
+      <c r="O10" s="63" t="s">
         <v>188</v>
       </c>
-      <c r="P10" s="72">
+      <c r="P10" s="64">
         <v>7.7000000000000002E-3</v>
       </c>
-      <c r="Q10" s="72">
+      <c r="Q10" s="64">
         <f>P10*N10</f>
         <v>1.155</v>
       </c>
@@ -2102,7 +2102,7 @@
         <f t="shared" ref="B11:B43" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="67" t="s">
+      <c r="C11" s="59" t="s">
         <v>166</v>
       </c>
       <c r="D11" s="50" t="s">
@@ -2132,20 +2132,20 @@
       <c r="L11" s="51">
         <v>2</v>
       </c>
-      <c r="M11" s="70">
+      <c r="M11" s="62">
         <f t="shared" ref="M11:M43" si="1">L11*6</f>
         <v>12</v>
       </c>
       <c r="N11" s="50">
         <v>15</v>
       </c>
-      <c r="O11" s="74" t="s">
+      <c r="O11" s="66" t="s">
         <v>188</v>
       </c>
-      <c r="P11" s="73">
+      <c r="P11" s="65">
         <v>8.4199999999999997E-2</v>
       </c>
-      <c r="Q11" s="75">
+      <c r="Q11" s="67">
         <f t="shared" ref="Q11:Q43" si="2">P11*N11</f>
         <v>1.2629999999999999</v>
       </c>
@@ -2158,7 +2158,7 @@
         <f>ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
-      <c r="C12" s="66" t="s">
+      <c r="C12" s="58" t="s">
         <v>166</v>
       </c>
       <c r="D12" s="46" t="s">
@@ -2195,18 +2195,18 @@
       <c r="N12" s="46">
         <v>40</v>
       </c>
-      <c r="O12" s="71" t="s">
+      <c r="O12" s="63" t="s">
         <v>188</v>
       </c>
-      <c r="P12" s="72">
+      <c r="P12" s="64">
         <v>3.49E-2</v>
       </c>
-      <c r="Q12" s="72">
+      <c r="Q12" s="64">
         <f t="shared" si="2"/>
         <v>1.3959999999999999</v>
       </c>
       <c r="R12" s="48"/>
-      <c r="S12" s="69"/>
+      <c r="S12" s="61"/>
     </row>
     <row r="13" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
@@ -2214,7 +2214,7 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="67" t="s">
+      <c r="C13" s="59" t="s">
         <v>166</v>
       </c>
       <c r="D13" s="50" t="s">
@@ -2244,20 +2244,20 @@
       <c r="L13" s="51">
         <v>3</v>
       </c>
-      <c r="M13" s="70">
+      <c r="M13" s="62">
         <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="N13" s="50">
         <v>50</v>
       </c>
-      <c r="O13" s="74" t="s">
+      <c r="O13" s="66" t="s">
         <v>188</v>
       </c>
-      <c r="P13" s="73">
+      <c r="P13" s="65">
         <v>5.4999999999999997E-3</v>
       </c>
-      <c r="Q13" s="75">
+      <c r="Q13" s="67">
         <f t="shared" si="2"/>
         <v>0.27499999999999997</v>
       </c>
@@ -2270,7 +2270,7 @@
         <f>ROW(B14) - ROW($B$9)</f>
         <v>5</v>
       </c>
-      <c r="C14" s="66" t="s">
+      <c r="C14" s="58" t="s">
         <v>166</v>
       </c>
       <c r="D14" s="46" t="s">
@@ -2307,18 +2307,18 @@
       <c r="N14" s="46">
         <v>100</v>
       </c>
-      <c r="O14" s="71" t="s">
+      <c r="O14" s="63" t="s">
         <v>188</v>
       </c>
-      <c r="P14" s="72">
+      <c r="P14" s="64">
         <v>7.6E-3</v>
       </c>
-      <c r="Q14" s="72">
+      <c r="Q14" s="64">
         <f t="shared" si="2"/>
         <v>0.76</v>
       </c>
       <c r="R14" s="48"/>
-      <c r="S14" s="69"/>
+      <c r="S14" s="61"/>
     </row>
     <row r="15" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
@@ -2326,7 +2326,7 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="67" t="s">
+      <c r="C15" s="59" t="s">
         <v>166</v>
       </c>
       <c r="D15" s="50" t="s">
@@ -2356,20 +2356,20 @@
       <c r="L15" s="51">
         <v>3</v>
       </c>
-      <c r="M15" s="70">
+      <c r="M15" s="62">
         <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="N15" s="50">
         <v>50</v>
       </c>
-      <c r="O15" s="74" t="s">
+      <c r="O15" s="66" t="s">
         <v>188</v>
       </c>
-      <c r="P15" s="73">
+      <c r="P15" s="65">
         <v>8.0999999999999996E-3</v>
       </c>
-      <c r="Q15" s="75">
+      <c r="Q15" s="67">
         <f t="shared" si="2"/>
         <v>0.40499999999999997</v>
       </c>
@@ -2382,7 +2382,7 @@
         <f>ROW(B16) - ROW($B$9)</f>
         <v>7</v>
       </c>
-      <c r="C16" s="66" t="s">
+      <c r="C16" s="58" t="s">
         <v>166</v>
       </c>
       <c r="D16" s="46" t="s">
@@ -2394,7 +2394,7 @@
       <c r="F16" s="46" t="s">
         <v>80</v>
       </c>
-      <c r="G16" s="77" t="s">
+      <c r="G16" s="69" t="s">
         <v>104</v>
       </c>
       <c r="H16" s="46" t="s">
@@ -2419,18 +2419,18 @@
       <c r="N16" s="46">
         <v>50</v>
       </c>
-      <c r="O16" s="71" t="s">
+      <c r="O16" s="63" t="s">
         <v>188</v>
       </c>
-      <c r="P16" s="72">
+      <c r="P16" s="64">
         <v>5.3E-3</v>
       </c>
-      <c r="Q16" s="72">
+      <c r="Q16" s="64">
         <f t="shared" si="2"/>
         <v>0.26500000000000001</v>
       </c>
       <c r="R16" s="48"/>
-      <c r="S16" s="69"/>
+      <c r="S16" s="61"/>
     </row>
     <row r="17" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
@@ -2438,7 +2438,7 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="67" t="s">
+      <c r="C17" s="59" t="s">
         <v>166</v>
       </c>
       <c r="D17" s="50" t="s">
@@ -2468,20 +2468,20 @@
       <c r="L17" s="51">
         <v>2</v>
       </c>
-      <c r="M17" s="70">
+      <c r="M17" s="62">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="N17" s="50">
         <v>50</v>
       </c>
-      <c r="O17" s="74" t="s">
+      <c r="O17" s="66" t="s">
         <v>188</v>
       </c>
-      <c r="P17" s="73">
+      <c r="P17" s="65">
         <v>6.3E-3</v>
       </c>
-      <c r="Q17" s="75">
+      <c r="Q17" s="67">
         <f t="shared" si="2"/>
         <v>0.315</v>
       </c>
@@ -2494,7 +2494,7 @@
         <f>ROW(B18) - ROW($B$9)</f>
         <v>9</v>
       </c>
-      <c r="C18" s="66" t="s">
+      <c r="C18" s="58" t="s">
         <v>166</v>
       </c>
       <c r="D18" s="46" t="s">
@@ -2531,18 +2531,18 @@
       <c r="N18" s="46">
         <v>100</v>
       </c>
-      <c r="O18" s="71" t="s">
+      <c r="O18" s="63" t="s">
         <v>188</v>
       </c>
-      <c r="P18" s="72">
+      <c r="P18" s="64">
         <v>3.3E-3</v>
       </c>
-      <c r="Q18" s="72">
+      <c r="Q18" s="64">
         <f t="shared" si="2"/>
         <v>0.33</v>
       </c>
       <c r="R18" s="48"/>
-      <c r="S18" s="69"/>
+      <c r="S18" s="61"/>
     </row>
     <row r="19" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
@@ -2550,7 +2550,7 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="67" t="s">
+      <c r="C19" s="59" t="s">
         <v>166</v>
       </c>
       <c r="D19" s="50" t="s">
@@ -2580,20 +2580,20 @@
       <c r="L19" s="51">
         <v>3</v>
       </c>
-      <c r="M19" s="70">
+      <c r="M19" s="62">
         <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="N19" s="50">
         <v>20</v>
       </c>
-      <c r="O19" s="74" t="s">
+      <c r="O19" s="66" t="s">
         <v>188</v>
       </c>
-      <c r="P19" s="73">
+      <c r="P19" s="65">
         <v>0.14849999999999999</v>
       </c>
-      <c r="Q19" s="75">
+      <c r="Q19" s="67">
         <f t="shared" si="2"/>
         <v>2.9699999999999998</v>
       </c>
@@ -2606,7 +2606,7 @@
         <f>ROW(B20) - ROW($B$9)</f>
         <v>11</v>
       </c>
-      <c r="C20" s="66" t="s">
+      <c r="C20" s="58" t="s">
         <v>167</v>
       </c>
       <c r="D20" s="46" t="s">
@@ -2618,7 +2618,7 @@
       <c r="F20" s="46" t="s">
         <v>82</v>
       </c>
-      <c r="G20" s="77">
+      <c r="G20" s="69">
         <v>742792651</v>
       </c>
       <c r="H20" s="46" t="s">
@@ -2643,18 +2643,18 @@
       <c r="N20" s="46">
         <v>100</v>
       </c>
-      <c r="O20" s="71" t="s">
+      <c r="O20" s="63" t="s">
         <v>188</v>
       </c>
-      <c r="P20" s="72">
+      <c r="P20" s="64">
         <v>4.1000000000000003E-3</v>
       </c>
-      <c r="Q20" s="72">
+      <c r="Q20" s="64">
         <f t="shared" si="2"/>
         <v>0.41000000000000003</v>
       </c>
       <c r="R20" s="48"/>
-      <c r="S20" s="69"/>
+      <c r="S20" s="61"/>
     </row>
     <row r="21" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
@@ -2662,7 +2662,7 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C21" s="67" t="s">
+      <c r="C21" s="59" t="s">
         <v>168</v>
       </c>
       <c r="D21" s="50" t="s">
@@ -2692,20 +2692,20 @@
       <c r="L21" s="51">
         <v>1</v>
       </c>
-      <c r="M21" s="70">
+      <c r="M21" s="62">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="N21" s="50">
         <v>20</v>
       </c>
-      <c r="O21" s="74" t="s">
+      <c r="O21" s="66" t="s">
         <v>188</v>
       </c>
-      <c r="P21" s="73">
+      <c r="P21" s="65">
         <v>2.3400000000000001E-2</v>
       </c>
-      <c r="Q21" s="75">
+      <c r="Q21" s="67">
         <f t="shared" si="2"/>
         <v>0.46800000000000003</v>
       </c>
@@ -2718,7 +2718,7 @@
         <f>ROW(B22) - ROW($B$9)</f>
         <v>13</v>
       </c>
-      <c r="C22" s="66" t="s">
+      <c r="C22" s="58" t="s">
         <v>168</v>
       </c>
       <c r="D22" s="46" t="s">
@@ -2742,7 +2742,7 @@
       <c r="J22" s="46" t="s">
         <v>198</v>
       </c>
-      <c r="K22" s="68" t="s">
+      <c r="K22" s="60" t="s">
         <v>179</v>
       </c>
       <c r="L22" s="47">
@@ -2755,18 +2755,18 @@
       <c r="N22" s="46">
         <v>10</v>
       </c>
-      <c r="O22" s="71" t="s">
+      <c r="O22" s="63" t="s">
         <v>188</v>
       </c>
-      <c r="P22" s="72">
+      <c r="P22" s="64">
         <v>4.4699999999999997E-2</v>
       </c>
-      <c r="Q22" s="72">
+      <c r="Q22" s="64">
         <f t="shared" si="2"/>
         <v>0.44699999999999995</v>
       </c>
       <c r="R22" s="48"/>
-      <c r="S22" s="69"/>
+      <c r="S22" s="61"/>
     </row>
     <row r="23" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
@@ -2774,7 +2774,7 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C23" s="67" t="s">
+      <c r="C23" s="59" t="s">
         <v>169</v>
       </c>
       <c r="D23" s="50" t="s">
@@ -2786,7 +2786,7 @@
       <c r="F23" s="50" t="s">
         <v>85</v>
       </c>
-      <c r="G23" s="76">
+      <c r="G23" s="68">
         <v>61300311121</v>
       </c>
       <c r="H23" s="50" t="s">
@@ -2804,20 +2804,20 @@
       <c r="L23" s="51">
         <v>1</v>
       </c>
-      <c r="M23" s="70">
+      <c r="M23" s="62">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="N23" s="50">
         <v>50</v>
       </c>
-      <c r="O23" s="74" t="s">
+      <c r="O23" s="66" t="s">
         <v>188</v>
       </c>
-      <c r="P23" s="73">
+      <c r="P23" s="65">
         <v>1.8700000000000001E-2</v>
       </c>
-      <c r="Q23" s="75">
+      <c r="Q23" s="67">
         <f t="shared" si="2"/>
         <v>0.93500000000000005</v>
       </c>
@@ -2830,7 +2830,7 @@
         <f>ROW(B24) - ROW($B$9)</f>
         <v>15</v>
       </c>
-      <c r="C24" s="66" t="s">
+      <c r="C24" s="58" t="s">
         <v>169</v>
       </c>
       <c r="D24" s="46" t="s">
@@ -2842,7 +2842,7 @@
       <c r="F24" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="G24" s="77">
+      <c r="G24" s="69">
         <v>61300511121</v>
       </c>
       <c r="H24" s="46" t="s">
@@ -2867,18 +2867,18 @@
       <c r="N24" s="46">
         <v>20</v>
       </c>
-      <c r="O24" s="71" t="s">
+      <c r="O24" s="63" t="s">
         <v>188</v>
       </c>
-      <c r="P24" s="72">
+      <c r="P24" s="64">
         <v>3.2599999999999997E-2</v>
       </c>
-      <c r="Q24" s="72">
+      <c r="Q24" s="64">
         <f t="shared" si="2"/>
         <v>0.65199999999999991</v>
       </c>
       <c r="R24" s="48"/>
-      <c r="S24" s="69"/>
+      <c r="S24" s="61"/>
     </row>
     <row r="25" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
@@ -2886,7 +2886,7 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C25" s="67" t="s">
+      <c r="C25" s="59" t="s">
         <v>169</v>
       </c>
       <c r="D25" s="50" t="s">
@@ -2898,7 +2898,7 @@
       <c r="F25" s="50" t="s">
         <v>87</v>
       </c>
-      <c r="G25" s="76">
+      <c r="G25" s="68">
         <v>61300711121</v>
       </c>
       <c r="H25" s="50" t="s">
@@ -2916,20 +2916,20 @@
       <c r="L25" s="51">
         <v>2</v>
       </c>
-      <c r="M25" s="70">
+      <c r="M25" s="62">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="N25" s="50">
         <v>20</v>
       </c>
-      <c r="O25" s="74" t="s">
+      <c r="O25" s="66" t="s">
         <v>188</v>
       </c>
-      <c r="P25" s="73">
+      <c r="P25" s="65">
         <v>3.85E-2</v>
       </c>
-      <c r="Q25" s="75">
+      <c r="Q25" s="67">
         <f t="shared" si="2"/>
         <v>0.77</v>
       </c>
@@ -2942,7 +2942,7 @@
         <f>ROW(B26) - ROW($B$9)</f>
         <v>17</v>
       </c>
-      <c r="C26" s="66" t="s">
+      <c r="C26" s="58" t="s">
         <v>169</v>
       </c>
       <c r="D26" s="46" t="s">
@@ -2954,7 +2954,7 @@
       <c r="F26" s="46" t="s">
         <v>88</v>
       </c>
-      <c r="G26" s="77">
+      <c r="G26" s="69">
         <v>61300411121</v>
       </c>
       <c r="H26" s="46" t="s">
@@ -2979,18 +2979,18 @@
       <c r="N26" s="46">
         <v>20</v>
       </c>
-      <c r="O26" s="71" t="s">
+      <c r="O26" s="63" t="s">
         <v>188</v>
       </c>
-      <c r="P26" s="72">
+      <c r="P26" s="64">
         <v>2.5499999999999998E-2</v>
       </c>
-      <c r="Q26" s="72">
+      <c r="Q26" s="64">
         <f t="shared" si="2"/>
         <v>0.51</v>
       </c>
       <c r="R26" s="48"/>
-      <c r="S26" s="69"/>
+      <c r="S26" s="61"/>
     </row>
     <row r="27" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
@@ -2998,7 +2998,7 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="C27" s="67" t="s">
+      <c r="C27" s="59" t="s">
         <v>169</v>
       </c>
       <c r="D27" s="50" t="s">
@@ -3010,7 +3010,7 @@
       <c r="F27" s="50" t="s">
         <v>89</v>
       </c>
-      <c r="G27" s="76" t="s">
+      <c r="G27" s="68" t="s">
         <v>109</v>
       </c>
       <c r="H27" s="50" t="s">
@@ -3028,20 +3028,20 @@
       <c r="L27" s="51">
         <v>1</v>
       </c>
-      <c r="M27" s="70">
+      <c r="M27" s="62">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="N27" s="50">
         <v>10</v>
       </c>
-      <c r="O27" s="74" t="s">
+      <c r="O27" s="66" t="s">
         <v>188</v>
       </c>
-      <c r="P27" s="73">
+      <c r="P27" s="65">
         <v>6.7799999999999999E-2</v>
       </c>
-      <c r="Q27" s="75">
+      <c r="Q27" s="67">
         <f t="shared" si="2"/>
         <v>0.67799999999999994</v>
       </c>
@@ -3054,7 +3054,7 @@
         <f>ROW(B28) - ROW($B$9)</f>
         <v>19</v>
       </c>
-      <c r="C28" s="66" t="s">
+      <c r="C28" s="58" t="s">
         <v>170</v>
       </c>
       <c r="D28" s="46" t="s">
@@ -3091,20 +3091,20 @@
       <c r="N28" s="46">
         <v>20</v>
       </c>
-      <c r="O28" s="71" t="s">
+      <c r="O28" s="63" t="s">
         <v>224</v>
       </c>
-      <c r="P28" s="72">
+      <c r="P28" s="64">
         <v>4.8600000000000003</v>
       </c>
-      <c r="Q28" s="72">
+      <c r="Q28" s="64">
         <f t="shared" si="2"/>
         <v>97.2</v>
       </c>
-      <c r="R28" s="78" t="s">
+      <c r="R28" s="70" t="s">
         <v>225</v>
       </c>
-      <c r="S28" s="69"/>
+      <c r="S28" s="61"/>
     </row>
     <row r="29" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
@@ -3112,7 +3112,7 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C29" s="67" t="s">
+      <c r="C29" s="59" t="s">
         <v>171</v>
       </c>
       <c r="D29" s="50" t="s">
@@ -3142,20 +3142,20 @@
       <c r="L29" s="51">
         <v>13</v>
       </c>
-      <c r="M29" s="70">
+      <c r="M29" s="62">
         <f t="shared" si="1"/>
         <v>78</v>
       </c>
       <c r="N29" s="50">
         <v>100</v>
       </c>
-      <c r="O29" s="74" t="s">
+      <c r="O29" s="66" t="s">
         <v>188</v>
       </c>
-      <c r="P29" s="73">
+      <c r="P29" s="65">
         <v>1.5E-3</v>
       </c>
-      <c r="Q29" s="75">
+      <c r="Q29" s="67">
         <f t="shared" si="2"/>
         <v>0.15</v>
       </c>
@@ -3168,7 +3168,7 @@
         <f>ROW(B30) - ROW($B$9)</f>
         <v>21</v>
       </c>
-      <c r="C30" s="66" t="s">
+      <c r="C30" s="58" t="s">
         <v>171</v>
       </c>
       <c r="D30" s="46" t="s">
@@ -3205,18 +3205,18 @@
       <c r="N30" s="46">
         <v>100</v>
       </c>
-      <c r="O30" s="71" t="s">
+      <c r="O30" s="63" t="s">
         <v>188</v>
       </c>
-      <c r="P30" s="72">
+      <c r="P30" s="64">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="Q30" s="72">
+      <c r="Q30" s="64">
         <f t="shared" si="2"/>
         <v>0.13</v>
       </c>
       <c r="R30" s="48"/>
-      <c r="S30" s="69"/>
+      <c r="S30" s="61"/>
     </row>
     <row r="31" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
@@ -3224,7 +3224,7 @@
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="C31" s="67" t="s">
+      <c r="C31" s="59" t="s">
         <v>171</v>
       </c>
       <c r="D31" s="50" t="s">
@@ -3254,20 +3254,20 @@
       <c r="L31" s="51">
         <v>7</v>
       </c>
-      <c r="M31" s="70">
+      <c r="M31" s="62">
         <f t="shared" si="1"/>
         <v>42</v>
       </c>
       <c r="N31" s="50">
         <v>50</v>
       </c>
-      <c r="O31" s="74" t="s">
+      <c r="O31" s="66" t="s">
         <v>188</v>
       </c>
-      <c r="P31" s="73">
+      <c r="P31" s="65">
         <v>7.3000000000000001E-3</v>
       </c>
-      <c r="Q31" s="75">
+      <c r="Q31" s="67">
         <f t="shared" si="2"/>
         <v>0.36499999999999999</v>
       </c>
@@ -3280,7 +3280,7 @@
         <f>ROW(B32) - ROW($B$9)</f>
         <v>23</v>
       </c>
-      <c r="C32" s="66" t="s">
+      <c r="C32" s="58" t="s">
         <v>171</v>
       </c>
       <c r="D32" s="46" t="s">
@@ -3317,18 +3317,18 @@
       <c r="N32" s="46">
         <v>100</v>
       </c>
-      <c r="O32" s="71" t="s">
+      <c r="O32" s="63" t="s">
         <v>188</v>
       </c>
-      <c r="P32" s="72">
+      <c r="P32" s="64">
         <v>1.5E-3</v>
       </c>
-      <c r="Q32" s="72">
+      <c r="Q32" s="64">
         <f t="shared" si="2"/>
         <v>0.15</v>
       </c>
       <c r="R32" s="48"/>
-      <c r="S32" s="69"/>
+      <c r="S32" s="61"/>
     </row>
     <row r="33" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
@@ -3336,7 +3336,7 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="C33" s="67" t="s">
+      <c r="C33" s="59" t="s">
         <v>171</v>
       </c>
       <c r="D33" s="50" t="s">
@@ -3366,20 +3366,20 @@
       <c r="L33" s="51">
         <v>1</v>
       </c>
-      <c r="M33" s="70">
+      <c r="M33" s="62">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="N33" s="50">
         <v>100</v>
       </c>
-      <c r="O33" s="74" t="s">
+      <c r="O33" s="66" t="s">
         <v>188</v>
       </c>
-      <c r="P33" s="73">
+      <c r="P33" s="65">
         <v>5.9999999999999995E-4</v>
       </c>
-      <c r="Q33" s="75">
+      <c r="Q33" s="67">
         <f t="shared" si="2"/>
         <v>0.06</v>
       </c>
@@ -3392,7 +3392,7 @@
         <f>ROW(B34) - ROW($B$9)</f>
         <v>25</v>
       </c>
-      <c r="C34" s="66" t="s">
+      <c r="C34" s="58" t="s">
         <v>171</v>
       </c>
       <c r="D34" s="46" t="s">
@@ -3429,18 +3429,18 @@
       <c r="N34" s="46">
         <v>100</v>
       </c>
-      <c r="O34" s="71" t="s">
+      <c r="O34" s="63" t="s">
         <v>188</v>
       </c>
-      <c r="P34" s="72">
+      <c r="P34" s="64">
         <v>1.4E-3</v>
       </c>
-      <c r="Q34" s="72">
+      <c r="Q34" s="64">
         <f t="shared" si="2"/>
         <v>0.13999999999999999</v>
       </c>
       <c r="R34" s="48"/>
-      <c r="S34" s="69"/>
+      <c r="S34" s="61"/>
     </row>
     <row r="35" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
@@ -3448,7 +3448,7 @@
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="C35" s="67" t="s">
+      <c r="C35" s="59" t="s">
         <v>171</v>
       </c>
       <c r="D35" s="50" t="s">
@@ -3478,20 +3478,20 @@
       <c r="L35" s="51">
         <v>1</v>
       </c>
-      <c r="M35" s="70">
+      <c r="M35" s="62">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="N35" s="50">
         <v>100</v>
       </c>
-      <c r="O35" s="74" t="s">
+      <c r="O35" s="66" t="s">
         <v>188</v>
       </c>
-      <c r="P35" s="73">
+      <c r="P35" s="65">
         <v>1.1000000000000001E-3</v>
       </c>
-      <c r="Q35" s="75">
+      <c r="Q35" s="67">
         <f t="shared" si="2"/>
         <v>0.11</v>
       </c>
@@ -3504,7 +3504,7 @@
         <f>ROW(B36) - ROW($B$9)</f>
         <v>27</v>
       </c>
-      <c r="C36" s="66" t="s">
+      <c r="C36" s="58" t="s">
         <v>171</v>
       </c>
       <c r="D36" s="46" t="s">
@@ -3541,18 +3541,18 @@
       <c r="N36" s="46">
         <v>100</v>
       </c>
-      <c r="O36" s="71" t="s">
+      <c r="O36" s="63" t="s">
         <v>188</v>
       </c>
-      <c r="P36" s="72">
+      <c r="P36" s="64">
         <v>3.5999999999999999E-3</v>
       </c>
-      <c r="Q36" s="72">
+      <c r="Q36" s="64">
         <f t="shared" si="2"/>
         <v>0.36</v>
       </c>
       <c r="R36" s="48"/>
-      <c r="S36" s="69"/>
+      <c r="S36" s="61"/>
     </row>
     <row r="37" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
@@ -3560,7 +3560,7 @@
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="C37" s="67" t="s">
+      <c r="C37" s="59" t="s">
         <v>171</v>
       </c>
       <c r="D37" s="50" t="s">
@@ -3590,20 +3590,20 @@
       <c r="L37" s="51">
         <v>2</v>
       </c>
-      <c r="M37" s="70">
+      <c r="M37" s="62">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="N37" s="50">
         <v>20</v>
       </c>
-      <c r="O37" s="74" t="s">
+      <c r="O37" s="66" t="s">
         <v>188</v>
       </c>
-      <c r="P37" s="73">
+      <c r="P37" s="65">
         <v>3.5700000000000003E-2</v>
       </c>
-      <c r="Q37" s="75">
+      <c r="Q37" s="67">
         <f t="shared" si="2"/>
         <v>0.71400000000000008</v>
       </c>
@@ -3616,7 +3616,7 @@
         <f>ROW(B38) - ROW($B$9)</f>
         <v>29</v>
       </c>
-      <c r="C38" s="66" t="s">
+      <c r="C38" s="58" t="s">
         <v>171</v>
       </c>
       <c r="D38" s="46" t="s">
@@ -3653,18 +3653,18 @@
       <c r="N38" s="46">
         <v>20</v>
       </c>
-      <c r="O38" s="71" t="s">
+      <c r="O38" s="63" t="s">
         <v>188</v>
       </c>
-      <c r="P38" s="72">
+      <c r="P38" s="64">
         <v>3.27E-2</v>
       </c>
-      <c r="Q38" s="72">
+      <c r="Q38" s="64">
         <f t="shared" si="2"/>
         <v>0.65400000000000003</v>
       </c>
       <c r="R38" s="48"/>
-      <c r="S38" s="69"/>
+      <c r="S38" s="61"/>
     </row>
     <row r="39" spans="1:19" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
@@ -3672,7 +3672,7 @@
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="C39" s="67" t="s">
+      <c r="C39" s="59" t="s">
         <v>172</v>
       </c>
       <c r="D39" s="50" t="s">
@@ -3702,24 +3702,24 @@
       <c r="L39" s="51">
         <v>1</v>
       </c>
-      <c r="M39" s="70">
+      <c r="M39" s="62">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="N39" s="50">
         <v>7</v>
       </c>
-      <c r="O39" s="74" t="s">
+      <c r="O39" s="66" t="s">
         <v>224</v>
       </c>
-      <c r="P39" s="73">
+      <c r="P39" s="65">
         <v>12.54</v>
       </c>
-      <c r="Q39" s="75">
+      <c r="Q39" s="67">
         <f t="shared" si="2"/>
         <v>87.78</v>
       </c>
-      <c r="R39" s="79" t="s">
+      <c r="R39" s="71" t="s">
         <v>225</v>
       </c>
       <c r="S39" s="53"/>
@@ -3730,7 +3730,7 @@
         <f>ROW(B40) - ROW($B$9)</f>
         <v>31</v>
       </c>
-      <c r="C40" s="66" t="s">
+      <c r="C40" s="58" t="s">
         <v>172</v>
       </c>
       <c r="D40" s="46" t="s">
@@ -3767,14 +3767,18 @@
       <c r="N40" s="46">
         <v>13</v>
       </c>
-      <c r="O40" s="46"/>
-      <c r="P40" s="72"/>
-      <c r="Q40" s="72">
+      <c r="O40" s="63" t="s">
+        <v>188</v>
+      </c>
+      <c r="P40" s="64">
+        <v>0.48870000000000002</v>
+      </c>
+      <c r="Q40" s="64">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>6.3531000000000004</v>
       </c>
       <c r="R40" s="48"/>
-      <c r="S40" s="69"/>
+      <c r="S40" s="61"/>
     </row>
     <row r="41" spans="1:19" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
@@ -3782,7 +3786,7 @@
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="C41" s="67" t="s">
+      <c r="C41" s="59" t="s">
         <v>172</v>
       </c>
       <c r="D41" s="50" t="s">
@@ -3812,24 +3816,24 @@
       <c r="L41" s="51">
         <v>1</v>
       </c>
-      <c r="M41" s="70">
+      <c r="M41" s="62">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="N41" s="50">
         <v>7</v>
       </c>
-      <c r="O41" s="74" t="s">
+      <c r="O41" s="66" t="s">
         <v>224</v>
       </c>
-      <c r="P41" s="73">
+      <c r="P41" s="65">
         <v>2.665</v>
       </c>
-      <c r="Q41" s="75">
+      <c r="Q41" s="67">
         <f t="shared" si="2"/>
         <v>18.655000000000001</v>
       </c>
-      <c r="R41" s="79" t="s">
+      <c r="R41" s="71" t="s">
         <v>225</v>
       </c>
       <c r="S41" s="53"/>
@@ -3840,7 +3844,7 @@
         <f>ROW(B42) - ROW($B$9)</f>
         <v>33</v>
       </c>
-      <c r="C42" s="66" t="s">
+      <c r="C42" s="58" t="s">
         <v>172</v>
       </c>
       <c r="D42" s="46" t="s">
@@ -3877,18 +3881,18 @@
       <c r="N42" s="46">
         <v>13</v>
       </c>
-      <c r="O42" s="71" t="s">
+      <c r="O42" s="63" t="s">
         <v>226</v>
       </c>
-      <c r="P42" s="72">
+      <c r="P42" s="64">
         <v>1.18</v>
       </c>
-      <c r="Q42" s="72">
+      <c r="Q42" s="64">
         <f t="shared" si="2"/>
         <v>15.34</v>
       </c>
-      <c r="R42" s="78"/>
-      <c r="S42" s="69"/>
+      <c r="R42" s="70"/>
+      <c r="S42" s="61"/>
     </row>
     <row r="43" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
@@ -3896,7 +3900,7 @@
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="C43" s="67" t="s">
+      <c r="C43" s="59" t="s">
         <v>173</v>
       </c>
       <c r="D43" s="50" t="s">
@@ -3926,20 +3930,20 @@
       <c r="L43" s="51">
         <v>1</v>
       </c>
-      <c r="M43" s="70">
+      <c r="M43" s="62">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="N43" s="50">
         <v>8</v>
       </c>
-      <c r="O43" s="74" t="s">
+      <c r="O43" s="66" t="s">
         <v>188</v>
       </c>
-      <c r="P43" s="73">
+      <c r="P43" s="65">
         <v>0.49049999999999999</v>
       </c>
-      <c r="Q43" s="75">
+      <c r="Q43" s="67">
         <f t="shared" si="2"/>
         <v>3.9239999999999999</v>
       </c>
@@ -3962,17 +3966,17 @@
       <c r="K44" s="37"/>
       <c r="L44" s="37"/>
       <c r="M44" s="37"/>
-      <c r="N44" s="80" t="s">
+      <c r="N44" s="74" t="s">
         <v>227</v>
       </c>
-      <c r="O44" s="81"/>
-      <c r="P44" s="81"/>
-      <c r="Q44" s="82">
+      <c r="O44" s="75"/>
+      <c r="P44" s="75"/>
+      <c r="Q44" s="72">
         <f>SUM(Q10:Q43)</f>
-        <v>239.73600000000002</v>
-      </c>
-      <c r="R44" s="62"/>
-      <c r="S44" s="63"/>
+        <v>246.08910000000003</v>
+      </c>
+      <c r="R44" s="80"/>
+      <c r="S44" s="81"/>
     </row>
     <row r="45" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1"/>
@@ -3990,25 +3994,25 @@
       <c r="K45" s="10"/>
       <c r="L45" s="10"/>
       <c r="M45" s="10"/>
-      <c r="N45" s="80" t="s">
+      <c r="N45" s="74" t="s">
         <v>228</v>
       </c>
-      <c r="O45" s="81"/>
-      <c r="P45" s="81"/>
-      <c r="Q45" s="83">
+      <c r="O45" s="75"/>
+      <c r="P45" s="75"/>
+      <c r="Q45" s="73">
         <f>Q44/5</f>
-        <v>47.947200000000002</v>
-      </c>
-      <c r="R45" s="64"/>
-      <c r="S45" s="65"/>
+        <v>49.217820000000003</v>
+      </c>
+      <c r="R45" s="82"/>
+      <c r="S45" s="83"/>
     </row>
     <row r="46" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="N46" s="80" t="s">
+      <c r="N46" s="74" t="s">
         <v>229</v>
       </c>
-      <c r="O46" s="81"/>
-      <c r="P46" s="81"/>
-      <c r="Q46" s="83">
+      <c r="O46" s="75"/>
+      <c r="P46" s="75"/>
+      <c r="Q46" s="73">
         <v>5</v>
       </c>
     </row>
@@ -4052,9 +4056,10 @@
     <hyperlink ref="O16" r:id="rId28" xr:uid="{C53CA0AB-9832-415A-B121-CBE94F0B89BD}"/>
     <hyperlink ref="O20" r:id="rId29" xr:uid="{3C80B6F7-5E64-47DC-B383-AFE2B8AECEAD}"/>
     <hyperlink ref="O42" r:id="rId30" xr:uid="{25D4EF2A-0C84-4D73-8BF4-4B215CC0FB78}"/>
+    <hyperlink ref="O40" r:id="rId31" xr:uid="{DBB7BEF9-30AB-415D-86DA-4EEB8C364B36}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId31"/>
-  <drawing r:id="rId32"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId32"/>
+  <drawing r:id="rId33"/>
 </worksheet>
 </file>
--- a/Deliverables/BOM/eSpark_BOM_Stepper_Breakout.xlsx
+++ b/Deliverables/BOM/eSpark_BOM_Stepper_Breakout.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25427"/>
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Mahmood-PTZKeyboard\Deliverables\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\Mahmood-PTZKeyboard\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38CA05D1-A33B-45CF-9B24-B933DE610589}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -725,7 +724,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0000"/>
@@ -1774,7 +1773,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:S46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1789,7 +1788,7 @@
     <col min="9" max="9" width="21.42578125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11" customWidth="1"/>
     <col min="13" max="13" width="17.28515625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="19.28515625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="13.42578125" bestFit="1" customWidth="1"/>
@@ -2977,7 +2976,7 @@
         <v>12</v>
       </c>
       <c r="N26" s="46">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="O26" s="63" t="s">
         <v>188</v>
@@ -2986,8 +2985,7 @@
         <v>2.5499999999999998E-2</v>
       </c>
       <c r="Q26" s="64">
-        <f t="shared" si="2"/>
-        <v>0.51</v>
+        <v>1.6</v>
       </c>
       <c r="R26" s="48"/>
       <c r="S26" s="61"/>
@@ -3973,7 +3971,7 @@
       <c r="P44" s="75"/>
       <c r="Q44" s="72">
         <f>SUM(Q10:Q43)</f>
-        <v>246.08910000000003</v>
+        <v>247.17910000000001</v>
       </c>
       <c r="R44" s="80"/>
       <c r="S44" s="81"/>
@@ -4001,7 +3999,7 @@
       <c r="P45" s="75"/>
       <c r="Q45" s="73">
         <f>Q44/5</f>
-        <v>49.217820000000003</v>
+        <v>49.43582</v>
       </c>
       <c r="R45" s="82"/>
       <c r="S45" s="83"/>
@@ -4026,37 +4024,37 @@
     <mergeCell ref="N45:P45"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="O10" r:id="rId1" xr:uid="{4C62280C-E820-4DA0-B075-2C4DC0E5E153}"/>
-    <hyperlink ref="O11" r:id="rId2" xr:uid="{8DB9AC23-D402-47E4-8E3A-C01EE51106EC}"/>
-    <hyperlink ref="O12" r:id="rId3" xr:uid="{E7D7808C-19A0-4D07-BBA2-25DD109AFDE6}"/>
-    <hyperlink ref="O13" r:id="rId4" xr:uid="{6AB55C25-874D-4DDC-A7CA-4A2603D11285}"/>
-    <hyperlink ref="O14" r:id="rId5" xr:uid="{956F2BCD-7DD4-4BF3-B0B5-08EA91A875AE}"/>
-    <hyperlink ref="O15" r:id="rId6" xr:uid="{1A925E14-B680-4A4C-933B-0CD7ECBAA455}"/>
-    <hyperlink ref="O17" r:id="rId7" xr:uid="{2616AA2E-8292-4D92-B9CF-05931317C2A3}"/>
-    <hyperlink ref="O18" r:id="rId8" xr:uid="{83B97024-4734-44BC-A0EF-63D489B25F20}"/>
-    <hyperlink ref="O19" r:id="rId9" xr:uid="{97172467-1EDB-4501-A4A9-A6FF06490A05}"/>
-    <hyperlink ref="O21" r:id="rId10" xr:uid="{595688B3-5A0C-4212-B09F-3719446D45D0}"/>
-    <hyperlink ref="O22" r:id="rId11" xr:uid="{FAE977EA-4551-41D9-B591-05510C08D3D3}"/>
-    <hyperlink ref="O29" r:id="rId12" xr:uid="{78314A77-3265-4E0D-9381-8779CD3E769C}"/>
-    <hyperlink ref="O30" r:id="rId13" xr:uid="{1865EBAA-F14A-4B7C-B3F8-817E3D5192AA}"/>
-    <hyperlink ref="O31" r:id="rId14" xr:uid="{AC8F7EBD-61A0-4F6E-9AA3-C1A94875C98B}"/>
-    <hyperlink ref="O32" r:id="rId15" xr:uid="{39A27655-CD16-436B-BE33-8936AB09ED27}"/>
-    <hyperlink ref="O33" r:id="rId16" xr:uid="{2B0F1507-5572-467E-8115-6982150E3D45}"/>
-    <hyperlink ref="O34" r:id="rId17" xr:uid="{8775BC45-CE2D-4DA3-912B-5927D0B11A84}"/>
-    <hyperlink ref="O35" r:id="rId18" xr:uid="{F5E32A50-BBA1-42EB-9870-02D2EA2D61B7}"/>
-    <hyperlink ref="O36" r:id="rId19" xr:uid="{FFEF208E-6932-4AE9-B044-179E7FCFF0B4}"/>
-    <hyperlink ref="O37" r:id="rId20" xr:uid="{729CC811-41C3-4342-B649-DA116216E2CC}"/>
-    <hyperlink ref="O38" r:id="rId21" xr:uid="{0254AC19-C267-4B9E-96CD-5CE32864448A}"/>
-    <hyperlink ref="O43" r:id="rId22" xr:uid="{8A9E0887-29EF-4D68-A5A8-F01E6A4D2BAE}"/>
-    <hyperlink ref="O23" r:id="rId23" xr:uid="{F20A0156-EA12-4FC5-9AEF-6F842E293898}"/>
-    <hyperlink ref="O24" r:id="rId24" xr:uid="{1773FECD-2D5F-4D58-89FB-F4839FBC66A5}"/>
-    <hyperlink ref="O25" r:id="rId25" xr:uid="{4BB7D7B7-A3EA-47B4-984F-C0474B6C0D07}"/>
-    <hyperlink ref="O26" r:id="rId26" xr:uid="{3BCC235A-8DA6-446F-83CE-7970F7568789}"/>
-    <hyperlink ref="O27" r:id="rId27" xr:uid="{01B30327-9762-489C-9970-EA3F7EE0026E}"/>
-    <hyperlink ref="O16" r:id="rId28" xr:uid="{C53CA0AB-9832-415A-B121-CBE94F0B89BD}"/>
-    <hyperlink ref="O20" r:id="rId29" xr:uid="{3C80B6F7-5E64-47DC-B383-AFE2B8AECEAD}"/>
-    <hyperlink ref="O42" r:id="rId30" xr:uid="{25D4EF2A-0C84-4D73-8BF4-4B215CC0FB78}"/>
-    <hyperlink ref="O40" r:id="rId31" xr:uid="{DBB7BEF9-30AB-415D-86DA-4EEB8C364B36}"/>
+    <hyperlink ref="O10" r:id="rId1"/>
+    <hyperlink ref="O11" r:id="rId2"/>
+    <hyperlink ref="O12" r:id="rId3"/>
+    <hyperlink ref="O13" r:id="rId4"/>
+    <hyperlink ref="O14" r:id="rId5"/>
+    <hyperlink ref="O15" r:id="rId6"/>
+    <hyperlink ref="O17" r:id="rId7"/>
+    <hyperlink ref="O18" r:id="rId8"/>
+    <hyperlink ref="O19" r:id="rId9"/>
+    <hyperlink ref="O21" r:id="rId10"/>
+    <hyperlink ref="O22" r:id="rId11"/>
+    <hyperlink ref="O29" r:id="rId12"/>
+    <hyperlink ref="O30" r:id="rId13"/>
+    <hyperlink ref="O31" r:id="rId14"/>
+    <hyperlink ref="O32" r:id="rId15"/>
+    <hyperlink ref="O33" r:id="rId16"/>
+    <hyperlink ref="O34" r:id="rId17"/>
+    <hyperlink ref="O35" r:id="rId18"/>
+    <hyperlink ref="O36" r:id="rId19"/>
+    <hyperlink ref="O37" r:id="rId20"/>
+    <hyperlink ref="O38" r:id="rId21"/>
+    <hyperlink ref="O43" r:id="rId22"/>
+    <hyperlink ref="O23" r:id="rId23"/>
+    <hyperlink ref="O24" r:id="rId24"/>
+    <hyperlink ref="O25" r:id="rId25"/>
+    <hyperlink ref="O26" r:id="rId26"/>
+    <hyperlink ref="O27" r:id="rId27"/>
+    <hyperlink ref="O16" r:id="rId28"/>
+    <hyperlink ref="O20" r:id="rId29"/>
+    <hyperlink ref="O42" r:id="rId30"/>
+    <hyperlink ref="O40" r:id="rId31"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId32"/>
